--- a/構想_システム方式設計/AndroidControllerアプリ_方式設計資料.xlsx
+++ b/構想_システム方式設計/AndroidControllerアプリ_方式設計資料.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RcCarProject\構想_システム方式設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89B77C9-4664-4A0B-A477-75452A4FD516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5C943-5144-4B53-9D52-D95AA0AC0916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{8AAEB4EB-C378-4F37-812C-8D38BF53BD56}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{8AAEB4EB-C378-4F37-812C-8D38BF53BD56}"/>
   </bookViews>
   <sheets>
     <sheet name="はじめに" sheetId="1" r:id="rId1"/>
     <sheet name="アプリケーション構成について" sheetId="2" r:id="rId2"/>
     <sheet name="通信形式と状態遷移について" sheetId="3" r:id="rId3"/>
-    <sheet name="UI設計について" sheetId="4" r:id="rId4"/>
+    <sheet name="UI設計" sheetId="4" r:id="rId4"/>
+    <sheet name="ViewModel設計" sheetId="5" r:id="rId5"/>
+    <sheet name="通信Wrapper設計" sheetId="6" r:id="rId6"/>
+    <sheet name="BlueTooth通信層" sheetId="7" r:id="rId7"/>
+    <sheet name="異常系" sheetId="8" r:id="rId8"/>
+    <sheet name="テスト戦略" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">UI設計について!$A$1:$T$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">BlueTooth通信層!$A$1:$I$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">UI設計!$A$1:$T$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">ViewModel設計!$A$1:$F$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">アプリケーション構成について!$A$1:$S$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">テスト戦略!$A$1:$K$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">はじめに!$A$1:$K$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">異常系!$A$1:$K$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">通信Wrapper設計!$A$1:$K$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">通信形式と状態遷移について!$A$1:$Q$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="153">
   <si>
     <t>はじめに</t>
     <phoneticPr fontId="1"/>
@@ -358,13 +369,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>UI設計について</t>
-    <rPh sb="2" eb="4">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>★ ポイントは、未接続状態から異常状態には遷移しないこと</t>
     <rPh sb="8" eb="13">
       <t>ミセツゾクジョウタイ</t>
@@ -622,6 +626,840 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ViewModel設計</t>
+    <rPh sb="9" eb="11">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各種IFは以下のように定義する</t>
+    <rPh sb="0" eb="2">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fun  connect()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fun  disconncect()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>val connectionState: StateFlow&lt;ConnectionState&gt;</t>
+  </si>
+  <si>
+    <t>接続メソッド</t>
+    <rPh sb="0" eb="2">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切断メソッド</t>
+    <rPh sb="0" eb="2">
+      <t>セツダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enum class ConnectionState {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DISCONNECTED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONNECTING,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONNECTED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ERROR</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>通信状態格納定数</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信状態列挙 enum</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>レッキョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 通信確立メソッド群</t>
+    <rPh sb="2" eb="4">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>グン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ コントローラー操作メソッド群</t>
+    <rPh sb="9" eb="11">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>グン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fun moveForward()</t>
+  </si>
+  <si>
+    <t>fun moveBackward()</t>
+  </si>
+  <si>
+    <t>fun turnLeft()</t>
+  </si>
+  <si>
+    <t>fun turnRight()</t>
+  </si>
+  <si>
+    <t>fun stop()</t>
+  </si>
+  <si>
+    <t>fun setSpeed(value: Int)   // スライダー用</t>
+  </si>
+  <si>
+    <t>fun setDirection(x: Float, y: Float)  // ジョイスティック用</t>
+  </si>
+  <si>
+    <t>前進メソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後退メソッド</t>
+    <rPh sb="0" eb="2">
+      <t>コウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左回転メソッド</t>
+    <rPh sb="0" eb="3">
+      <t>ヒダリカイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右回転メソッド</t>
+    <rPh sb="0" eb="3">
+      <t>ミギカイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>停止メソッド</t>
+    <rPh sb="0" eb="2">
+      <t>テイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ こちらのメソッドの基本方針としては、以下とする。</t>
+    <rPh sb="11" eb="15">
+      <t>キホンホウシン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各種操作メソッドが呼ばれたらその中で 方向を設定するメソッドを呼び出して移動をさせること</t>
+    <rPh sb="0" eb="2">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 内部状態を格納するためのメソッド</t>
+    <rPh sb="2" eb="4">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>val batteryLevel: StateFlow&lt;Int&gt;</t>
+  </si>
+  <si>
+    <t>val temperature: StateFlow&lt;Float&gt;</t>
+  </si>
+  <si>
+    <t>val errorCode: StateFlow&lt;Int?&gt;</t>
+  </si>
+  <si>
+    <t>　 DISCONNECTING</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>interface CommunicationWrapper {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suspend fun connect(target: ConnectionTarget)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suspend fun disconnect()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suspend fun send(command: Command)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val connectionState: StateFlow&lt;ConnectionState&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val receivedData: StateFlow&lt;ReceivedData&gt;</t>
+  </si>
+  <si>
+    <t>通信Wrapper実現例</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ジツゲンレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sealed class ConnectionTarget {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    data class Bluetooth(val device: BluetoothDevice) : ConnectionTarget()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    data class Wifi(val ip: String, val port: Int) : ConnectionTarget()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    data class WebSocket(val url: String) : ConnectionTarget()</t>
+  </si>
+  <si>
+    <t>BlueTooth通信層</t>
+    <rPh sb="9" eb="11">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI設計</t>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data class Command(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val directionX: Float,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val directionY: Float,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val speed: Int</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t>★ 通信Wrapperインターフェース</t>
+    <rPh sb="2" eb="4">
+      <t>ツウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ コマンドクラス ※ こちらは接続媒体にかかわらず設定</t>
+    <rPh sb="16" eb="18">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バイタイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 接続ターゲットクラス ※ こちらについては拡張性を持たせる意図あり</t>
+    <rPh sb="2" eb="4">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクチョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data class ReceivedData(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val battery: Int?,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val temperature: Float?,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val errorCode: Int?</t>
+  </si>
+  <si>
+    <t>★ Rasberry Pi から受け取った通信状態について</t>
+    <rPh sb="16" eb="17">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>interface CommunicationClient {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suspend fun send(bytes: ByteArray)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val incomingData: Flow&lt;ByteArray&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    val state: StateFlow&lt;ConnectionState&gt;</t>
+  </si>
+  <si>
+    <t>★ 仮想クライアントの抽象化　(こちらはそれぞれの通信層の抽象クラスとなる)</t>
+    <rPh sb="2" eb="4">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>チュウショウカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>チュウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>class BluetoothClient : CommunicationClient {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    override suspend fun connect(target: ConnectionTarget) { ... }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    override suspend fun disconnect() { ... }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    override suspend fun send(bytes: ByteArray) { ... }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    override val incomingData: Flow&lt;ByteArray&gt; = ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    override val state: StateFlow&lt;ConnectionState&gt; = ...</t>
+  </si>
+  <si>
+    <t>★ BlueToothCient (これが実際の通信となる)</t>
+    <rPh sb="21" eb="23">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ツウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常系は以下のケースを定義するものとする</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① 接続失敗</t>
+    <rPh sb="2" eb="4">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>② データ送信失敗</t>
+    <rPh sb="5" eb="7">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ 受信データが壊れている</t>
+    <rPh sb="2" eb="4">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④ Bluetoothの接続が切れる</t>
+    <rPh sb="12" eb="14">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤ RasberryPiが応答しない</t>
+    <rPh sb="13" eb="15">
+      <t>オウトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ Android → RasberryPi のConnectに失敗した場合</t>
+    <rPh sb="32" eb="34">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ Connectは成立しているのが前提でその後の通信処理に失敗している場合</t>
+    <rPh sb="10" eb="12">
+      <t>セイリツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ RasberryPiから受信するデータの内容が不正な場合</t>
+    <rPh sb="14" eb="16">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フセイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 通信処理を実行していないタイミングにて応答がなくなった場合</t>
+    <rPh sb="2" eb="4">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウトウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ Controllerのメソッドの実行は成功したが、RasberryPi側が応答しない場合</t>
+    <rPh sb="18" eb="20">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>オウトウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストについては以下の方式で行うものとする</t>
+    <rPh sb="8" eb="10">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI層・・Espresso</t>
+    <rPh sb="2" eb="3">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ViewModel・・Junit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bluetooth通信層・・実機テスト</t>
+    <rPh sb="9" eb="12">
+      <t>ツウシンソウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信Wrapper・・Junit</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bluetooth通信が切れたらどうなるか</t>
+    <rPh sb="9" eb="11">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①エラー状態に遷移する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>② エラーになったことをユーザーがUIを見ることで確認</t>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③ 「切断ボタン」を押すことでError → Disconnectedに遷移</t>
+    <rPh sb="3" eb="5">
+      <t>セツダン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④ その後は「接続ボタン」をおすことで接続処理リトライ</t>
+    <rPh sb="4" eb="5">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bluetoothの通信切断はどのように判断するか</t>
+    <rPh sb="10" eb="12">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツダン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信失敗した(アプリ側のソフトエラー)場合はそのままあきらめてエラーに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受信データの内容が破損していた場合はそのままあきらめてエラーに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハソン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信実行後、一定時間応答(おおよそ5秒)が返ってこなければエラーに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジッコウゴ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オウトウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれ、通信確立メソッド群であるconnect()・disConnect()メソッドの実行状態</t>
+    <rPh sb="5" eb="7">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>グン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>に合わせて、通信Wrapper層からイベントとしてViewModel・UIへ通知を投げることとする</t>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信状態の設計方式について</t>
+    <rPh sb="0" eb="4">
+      <t>ツウシンジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ 受信データ例：通信状態・RasberryPiから通知される各種ラジコンのStatus</t>
+    <rPh sb="2" eb="4">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カクシュ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -630,7 +1468,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,6 +1496,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -699,7 +1554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -715,7 +1570,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2078,7 +2936,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>接続完了状態</a:t>
+            <a:t>接続終了状態</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
@@ -3065,6 +3923,902 @@
             </a:rPr>
             <a:t>)</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D53A86-9165-2C25-E4F5-25C728419558}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1356360" y="1836420"/>
+          <a:ext cx="2659380" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" b="1"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E39F30-078C-58D7-5923-7FAABAC0C919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2686050" y="2743200"/>
+          <a:ext cx="0" cy="1150620"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F40299A8-AC52-4606-9888-BCB974C2B8BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1356360" y="3893820"/>
+          <a:ext cx="2659380" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" b="1"/>
+            <a:t>ViewModel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB33CCC6-3559-4CBF-9887-1D54851081C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2686050" y="4800600"/>
+          <a:ext cx="0" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56C7E0E1-4A3F-4C19-A9D0-5E794ADB42BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1356360" y="5943600"/>
+          <a:ext cx="2659380" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1"/>
+            <a:t>通信</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1"/>
+            <a:t>Wrapper</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1"/>
+            <a:t>層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A227A6C-F83D-453A-8894-B8DF5AFDD096}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="2"/>
+          <a:endCxn id="19" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2686050" y="6850380"/>
+          <a:ext cx="0" cy="1165860"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F128978-760C-4BB7-887A-21E8601AACD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1356360" y="8016240"/>
+          <a:ext cx="2659380" cy="906780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" b="1"/>
+            <a:t>Bluetooth</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1"/>
+            <a:t>通信層</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C73DCB-0DD0-F02F-3D7F-AE0C4FD77A0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1615440"/>
+          <a:ext cx="4015740" cy="1584960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4831403F-8749-4033-8824-5405977BDF35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="3657600"/>
+          <a:ext cx="4015740" cy="3451860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FB50437-C3CB-4F43-B581-2CBC74134547}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="693420" y="7749540"/>
+          <a:ext cx="4015740" cy="1584960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="吹き出し: 四角形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEDB08CA-DE97-2202-49B7-47CAF67A5BE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5059680" y="2065020"/>
+          <a:ext cx="1257300" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -103837"/>
+            <a:gd name="adj2" fmla="val 53350"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Espresso</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="吹き出し: 四角形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ACB497F-9DFB-409F-AEAE-7B511CB3100E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5052060" y="4099560"/>
+          <a:ext cx="1257300" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -103837"/>
+            <a:gd name="adj2" fmla="val 53350"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>JUnit</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="吹き出し: 四角形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A844E2-1E02-40CD-90BE-BD82A2C0D8AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5021580" y="8077200"/>
+          <a:ext cx="1257300" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -103837"/>
+            <a:gd name="adj2" fmla="val 53350"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>実機テスト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3391,6 +5145,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3562,12 +5317,12 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -3583,7 +5338,6 @@
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="D34" s="5"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.45">
@@ -3602,17 +5356,17 @@
     </row>
     <row r="63" spans="9:9" x14ac:dyDescent="0.45">
       <c r="I63" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="9:9" x14ac:dyDescent="0.45">
       <c r="I64" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="9:9" x14ac:dyDescent="0.45">
       <c r="I66" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3630,57 +5384,57 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="12:12" x14ac:dyDescent="0.45">
       <c r="L17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3689,4 +5443,742 @@
   <pageSetup paperSize="9" scale="43" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847F7037-9508-42C3-A987-385C4AB28B7F}">
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="8.796875" style="5"/>
+    <col min="3" max="3" width="51.59765625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C11" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C12" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C13" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C14" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C15" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C16" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C28" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C29" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B32" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C33" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C34" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C35" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BC56BE-F51C-48DC-B778-5ECCC5E05C9D}">
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="16384" width="8.796875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="26.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="26.4" x14ac:dyDescent="0.45">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="6"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B23" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B24" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B26" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B27" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B30" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B31" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B32" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B33" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B34" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B38" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B40" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B44" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B45" s="6"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B47" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B48" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="73" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DCB6D9-2A5C-4233-AC75-672B6A01F630}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="26.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="2"/>
+      <c r="B6" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2"/>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5441D6C8-5C5C-458E-8772-EE83E0370697}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C12" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576E6882-C0A2-49DF-A08D-2B825E870819}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B4" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B8" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>